--- a/Pytest_Demonstration/Datadriven_Excel/Excelfiles/logindata.xlsx
+++ b/Pytest_Demonstration/Datadriven_Excel/Excelfiles/logindata.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhars\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhars\Documents\Python_Selenium\Pytest_Demonstration\Datadriven_Excel\Excelfiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0B46893-E026-4362-9DAF-4E104E2DFAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11024758-3349-403D-AA22-C72773324754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6F0805A3-D153-4A3E-8D37-5624D9F9B000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>password</t>
   </si>
@@ -37,6 +37,12 @@
   </si>
   <si>
     <t>dharshan123</t>
+  </si>
+  <si>
+    <t>vetri123456</t>
+  </si>
+  <si>
+    <t>vetri1234</t>
   </si>
 </sst>
 </file>
@@ -418,10 +424,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
